--- a/artfynd/A 34449-2021 artfynd.xlsx
+++ b/artfynd/A 34449-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131561400</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34449-2021 artfynd.xlsx
+++ b/artfynd/A 34449-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131561400</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34449-2021 artfynd.xlsx
+++ b/artfynd/A 34449-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131561400</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34449-2021 artfynd.xlsx
+++ b/artfynd/A 34449-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131561400</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,6 +777,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125132562</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långberget, Långberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>632803</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6553208</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
